--- a/VerveStacks_ARE_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ARE_grids_kan/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA2EA38-CA12-44C3-AA9D-7DF88AC60E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E45DE0C-EA68-4836-A150-31555A274E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4082,7 +4082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BADC4D-B186-475D-8CCB-7F7D8A31CB41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7EBAE3-9BD1-4E21-8064-1418C262B711}">
   <dimension ref="B3:I141"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ARE_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E45DE0C-EA68-4836-A150-31555A274E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A7D1E2-46DC-4118-804F-42AD658938A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4082,7 +4082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7EBAE3-9BD1-4E21-8064-1418C262B711}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00888EBF-D712-4870-AF9D-7BDDF3AB889F}">
   <dimension ref="B3:I141"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ARE_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A7D1E2-46DC-4118-804F-42AD658938A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0854E81C-D01C-477C-B951-9C68960BF12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4082,7 +4082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00888EBF-D712-4870-AF9D-7BDDF3AB889F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0F2052-9279-447B-8F42-CED209DB78A0}">
   <dimension ref="B3:I141"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_ARE_grids_kan/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0854E81C-D01C-477C-B951-9C68960BF12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671FA654-318B-43D9-8A67-FD42A213D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="545">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1668,6 +1668,12 @@
   </si>
   <si>
     <t>grid node -- way/95099973-220</t>
+  </si>
+  <si>
+    <t>elc_stargate</t>
+  </si>
+  <si>
+    <t>electricity used in stargate</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1697,7 @@
     <numFmt numFmtId="175" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
     <numFmt numFmtId="176" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2062,6 +2068,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -3141,7 +3155,7 @@
     <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
@@ -3167,6 +3181,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="234"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="234" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="437">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{822ECCD2-03B4-4EB0-AADE-6DECEB39BB19}"/>
@@ -7686,7 +7701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S30"/>
+  <dimension ref="B3:S31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -8308,23 +8323,14 @@
       </c>
     </row>
     <row r="21" spans="2:19">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" t="s">
-        <v>198</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C21" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>25</v>
       </c>
       <c r="M21" t="s">
         <v>17</v>
@@ -8350,16 +8356,22 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
-        <v>196</v>
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
       </c>
       <c r="M22" t="s">
         <v>17</v>
@@ -8388,7 +8400,10 @@
         <v>193</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>194</v>
+      </c>
+      <c r="D23" t="s">
+        <v>195</v>
       </c>
       <c r="E23" t="s">
         <v>196</v>
@@ -8420,7 +8435,7 @@
         <v>193</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
         <v>196</v>
@@ -8448,6 +8463,15 @@
       </c>
     </row>
     <row r="25" spans="2:19">
+      <c r="B25" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" t="s">
+        <v>196</v>
+      </c>
       <c r="M25" t="s">
         <v>17</v>
       </c>
@@ -8493,38 +8517,38 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="2:19" ht="17.649999999999999" thickBot="1">
-      <c r="B28" s="3" t="s">
+    <row r="29" spans="2:19" ht="17.649999999999999" thickBot="1">
+      <c r="B29" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="2:19" ht="15" thickTop="1" thickBot="1">
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="2:19" ht="15" thickTop="1" thickBot="1">
+      <c r="B30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="30" spans="2:19">
-      <c r="B30" t="s">
+    <row r="31" spans="2:19">
+      <c r="B31" t="s">
         <v>218</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>217</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>216</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C334">
-    <sortCondition ref="C19:C334"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C335">
+    <sortCondition ref="C19:C335"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8585,7 +8609,7 @@
       </c>
       <c r="F12" s="8" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
-        <v>msy6_2050</v>
+        <v>msy12_2050</v>
       </c>
       <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
@@ -8652,8 +8676,7 @@
         <v>2030</v>
       </c>
       <c r="F16" s="6">
-        <f>F15+5</f>
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="G16" s="6">
         <f>G15+5</f>
@@ -8672,8 +8695,8 @@
         <v>2035</v>
       </c>
       <c r="F17" s="6">
-        <f>F16+5</f>
-        <v>2035</v>
+        <f>F16+3</f>
+        <v>2030</v>
       </c>
       <c r="G17" s="6">
         <f>G16+10</f>
@@ -8692,11 +8715,11 @@
         <v>2040</v>
       </c>
       <c r="F18" s="6">
-        <f>F17+5</f>
-        <v>2040</v>
+        <f t="shared" ref="F18:F28" si="3">F17+2</f>
+        <v>2032</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" ref="G18" si="3">G17+10</f>
+        <f t="shared" ref="G18" si="4">G17+10</f>
         <v>2050</v>
       </c>
     </row>
@@ -8712,8 +8735,8 @@
         <v>2045</v>
       </c>
       <c r="F19" s="6">
-        <f>F18+10</f>
-        <v>2050</v>
+        <f>F18+3</f>
+        <v>2035</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="14.25">
@@ -8727,6 +8750,10 @@
         <f t="shared" si="2"/>
         <v>2050</v>
       </c>
+      <c r="F20" s="6">
+        <f>F19+3</f>
+        <v>2038</v>
+      </c>
     </row>
     <row r="21" spans="2:7" ht="14.25">
       <c r="B21" s="9">
@@ -8735,6 +8762,10 @@
       <c r="D21" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="F21" s="6">
+        <f t="shared" si="3"/>
+        <v>2040</v>
+      </c>
     </row>
     <row r="22" spans="2:7" ht="14.25">
       <c r="B22" s="9">
@@ -8743,6 +8774,10 @@
       <c r="D22" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="F22" s="6">
+        <f>F21+3</f>
+        <v>2043</v>
+      </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
       <c r="B23" s="9">
@@ -8751,6 +8786,10 @@
       <c r="D23" s="6" t="s">
         <v>47</v>
       </c>
+      <c r="F23" s="6">
+        <f t="shared" si="3"/>
+        <v>2045</v>
+      </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
       <c r="B24" s="9">
@@ -8758,12 +8797,20 @@
       </c>
       <c r="D24" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="F24" s="6">
+        <f>F23+3</f>
+        <v>2048</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="3"/>
+        <v>2050</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.25">
